--- a/output/pdf_financials_xlsx/CSX.xlsx
+++ b/output/pdf_financials_xlsx/CSX.xlsx
@@ -1258,19 +1258,19 @@
         <v>-1.300147</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-1.212419</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-6.204354</v>
@@ -1546,19 +1546,19 @@
         <v>-1.300147</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.212419</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-6.204354</v>
@@ -1717,19 +1717,19 @@
         <v>-1.300147</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-1.212419</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-6.204354</v>
@@ -1892,19 +1892,19 @@
         <v>18.573529</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-20.6762</v>
+        <v>20.6762</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-31.21945</v>
+        <v>31.21945</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-31.183925</v>
+        <v>31.183925</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>40.413967</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-48.606725</v>
+        <v>48.606725</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>51.70295</v>
@@ -1949,19 +1949,19 @@
         <v>-1.300147</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-1.212419</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-6.204354</v>
@@ -2063,19 +2063,19 @@
         <v>-1.300147</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.212419</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-6.204354</v>
@@ -2205,19 +2205,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -6061,16 +6061,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.58284</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.79419</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.069427</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.311883</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.070923</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.91909</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>2.93395</v>
@@ -12638,7 +12638,11 @@
           <t>Share-based payment reserve 16b</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -15194,7 +15198,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16930,7 +16938,11 @@
           <t>Share-based payment reserve 15,16</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -35255,13 +35267,13 @@
         </is>
       </c>
       <c r="H285" s="5" t="n">
-        <v>1.03381</v>
+        <v>-1.03381</v>
       </c>
       <c r="I285" s="5" t="n">
-        <v>1.248778</v>
+        <v>-1.248778</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>1.247357</v>
+        <v>-1.247357</v>
       </c>
       <c r="K285" s="5" t="n">
         <v>-1.212419</v>
@@ -37209,7 +37221,7 @@
         </is>
       </c>
       <c r="L306" s="5" t="n">
-        <v>1.944269</v>
+        <v>-1.944269</v>
       </c>
       <c r="M306" s="5" t="n">
         <v>-6.204354</v>

--- a/output/pdf_financials_xlsx/CSX.xlsx
+++ b/output/pdf_financials_xlsx/CSX.xlsx
@@ -7855,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.144213</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.18916</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7910,10 +7910,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.144213</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.18916</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -20282,7 +20282,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CSX.xlsx
+++ b/output/pdf_financials_xlsx/CSX.xlsx
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.036894</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.056539</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.07031999999999999</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2032,19 +2032,19 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.217156</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.321785</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.297679</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.289359</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.059738</v>
       </c>
     </row>
     <row r="29">
@@ -2075,13 +2075,13 @@
         <v>-1.212419</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.944269</v>
+        <v>-1.907375</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-6.204354</v>
+        <v>-6.147815</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.771325</v>
+        <v>-3.701005</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.271044</v>
+        <v>-3.053888</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.639596</v>
+        <v>-2.317811</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.879791</v>
+        <v>-4.582112</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.088057</v>
+        <v>-3.798698</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.446175</v>
+        <v>-3.386437</v>
       </c>
     </row>
     <row r="30">
@@ -6516,31 +6516,31 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.036894</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.056539</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.07031999999999999</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.230735</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.217156</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.321785</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.297679</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.289359</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.059738</v>
       </c>
     </row>
     <row r="101">
@@ -17208,7 +17208,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -34298,7 +34302,11 @@
           <t>Depreciation of property and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -35688,7 +35696,11 @@
           <t>Depreciation of property and equipment (Note 10)</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -37374,7 +37386,11 @@
           <t>Depreciation of property and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
